--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/2014-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/2014-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{96749103-ABCE-4FCF-9679-E6CD8F85D887}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{14768649-273A-494D-8589-D327C684C774}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{59A09D0D-759C-424C-B1CA-FE13351C7B75}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{AAE4028B-39C3-4B49-887D-D47FCB62AB9C}"/>
   </bookViews>
   <sheets>
     <sheet name="2014-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1448,28 +1448,27 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FA604B0-7057-487A-9920-DBF72D0B48B7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E72AB75-6C32-4BA8-9854-6F32925B05B6}">
   <dimension ref="A1:X42"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="9.75" customWidth="1"/>
-    <col min="4" max="6" width="6" customWidth="1"/>
-    <col min="7" max="7" width="6.25" customWidth="1"/>
-    <col min="8" max="8" width="6" customWidth="1"/>
-    <col min="9" max="10" width="6.25" customWidth="1"/>
-    <col min="11" max="13" width="6" customWidth="1"/>
-    <col min="14" max="15" width="6.25" customWidth="1"/>
-    <col min="16" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.25" customWidth="1"/>
-    <col min="20" max="20" width="6" customWidth="1"/>
-    <col min="21" max="21" width="6.25" customWidth="1"/>
-    <col min="22" max="22" width="6" customWidth="1"/>
-    <col min="23" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="6.875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
@@ -1503,7 +1502,7 @@
       <c r="W1" s="28"/>
       <c r="X1" s="20"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
@@ -1539,7 +1538,7 @@
       <c r="W2" s="30"/>
       <c r="X2" s="31"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="21" t="s">
         <v>2</v>
       </c>
@@ -1591,7 +1590,7 @@
       </c>
       <c r="X3" s="34"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="23"/>
       <c r="B4" s="24"/>
       <c r="C4" s="7"/>
@@ -1659,7 +1658,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="35">
         <v>2024</v>
       </c>
@@ -1731,7 +1730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="37">
         <v>2023</v>
       </c>
@@ -1803,7 +1802,7 @@
         <v>0.57999999999999996</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="35">
         <v>2022</v>
       </c>
@@ -1875,7 +1874,7 @@
         <v>1.72</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="37">
         <v>2021</v>
       </c>
@@ -1947,7 +1946,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="35">
         <v>2020</v>
       </c>
@@ -2019,7 +2018,7 @@
         <v>2.29</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="37">
         <v>2019</v>
       </c>
@@ -2091,7 +2090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="35">
         <v>2018</v>
       </c>
@@ -2163,7 +2162,7 @@
         <v>1.1200000000000001</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="37">
         <v>2017</v>
       </c>
@@ -2235,7 +2234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="35">
         <v>2016</v>
       </c>
@@ -2307,7 +2306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="37">
         <v>2015</v>
       </c>
@@ -2379,7 +2378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="35">
         <v>2014</v>
       </c>
@@ -2451,7 +2450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="37">
         <v>2013</v>
       </c>
@@ -2523,7 +2522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="35">
         <v>2012</v>
       </c>
@@ -2595,7 +2594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="37">
         <v>2011</v>
       </c>
@@ -2667,7 +2666,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="35">
         <v>2010</v>
       </c>
@@ -2739,7 +2738,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="37">
         <v>2009</v>
       </c>
@@ -2811,7 +2810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="35">
         <v>2008</v>
       </c>
@@ -2883,7 +2882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="37">
         <v>2007</v>
       </c>
@@ -2955,7 +2954,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="35">
         <v>2006</v>
       </c>
@@ -3027,7 +3026,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="37">
         <v>2005</v>
       </c>
@@ -3099,7 +3098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="35">
         <v>2004</v>
       </c>
@@ -3171,7 +3170,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="37">
         <v>2003</v>
       </c>
@@ -3243,7 +3242,7 @@
         <v>7.23</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="35">
         <v>2002</v>
       </c>
@@ -3315,7 +3314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="37">
         <v>2001</v>
       </c>
@@ -3387,7 +3386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="35">
         <v>2000</v>
       </c>
@@ -3459,7 +3458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="37">
         <v>1999</v>
       </c>
@@ -3531,7 +3530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="35">
         <v>1998</v>
       </c>
@@ -3603,7 +3602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="37">
         <v>1997</v>
       </c>
@@ -3675,7 +3674,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="35">
         <v>1996</v>
       </c>
@@ -3747,7 +3746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="37">
         <v>1995</v>
       </c>
@@ -3819,7 +3818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="35">
         <v>1994</v>
       </c>
@@ -3891,7 +3890,7 @@
         <v>6.58</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="37">
         <v>1993</v>
       </c>
@@ -3963,7 +3962,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="35">
         <v>1992</v>
       </c>
@@ -4035,7 +4034,7 @@
         <v>6.49</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="37">
         <v>1991</v>
       </c>
@@ -4107,7 +4106,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="35">
         <v>1990</v>
       </c>
@@ -4179,7 +4178,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="37">
         <v>1989</v>
       </c>
@@ -4251,7 +4250,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="35">
         <v>1988</v>
       </c>
@@ -4323,7 +4322,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="37" t="s">
         <v>40</v>
       </c>
